--- a/FSMs/Lemmings_Test_Plan.xlsx
+++ b/FSMs/Lemmings_Test_Plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ov084f\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local Disk D\GIT_REPOS\HDLBits_Designs\FSMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FD5555A-0C14-4F6D-BABC-A4800C0193AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ECA51D-FFD8-44F7-9EA5-97F61BC8ED27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA2B75B7-BD82-4FF3-8B52-2D2A2EBB1E98}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13335" xr2:uid="{DA2B75B7-BD82-4FF3-8B52-2D2A2EBB1E98}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>Test Name</t>
   </si>
@@ -130,6 +119,62 @@
   </si>
   <si>
     <t>Assert "dig" while keeping "ground" asserted and "bump_left" or "bump_right" asserted.</t>
+  </si>
+  <si>
+    <t>lemming_fall_priority_over_walking_test</t>
+  </si>
+  <si>
+    <t>This ensures that Lemming prioritizes falling over walking.</t>
+  </si>
+  <si>
+    <t>Deassert "ground" while keeping "bump_left" or "bump_right" asserted.</t>
+  </si>
+  <si>
+    <t>lemming_after_fall_walk_left_test</t>
+  </si>
+  <si>
+    <t>lemming_after_fall_walk_right_test</t>
+  </si>
+  <si>
+    <t>This ensures that Lemming when reaches ground after falling, walks in left direction as before</t>
+  </si>
+  <si>
+    <t>Perform Device Reset by asserting areset signal.
+Apply delay.
+Deassert "ground" signal.
+Apply delay.
+Assert "ground" signal.</t>
+  </si>
+  <si>
+    <t>Verify output signal "walk_left" set to 1.
+Then, "aaah" set to 1, then "walk_left" set to 1 again.</t>
+  </si>
+  <si>
+    <t>Perform Device Reset by asserting areset signal.
+Assert "bump_left" signal.
+Apply delay.
+Deassert "ground" signal.
+Apply delay.
+Assert "ground" signal.</t>
+  </si>
+  <si>
+    <t>Verify output signal "walk_right" set to 1.
+Then, "aaah" set to 1, then "walk_right" set to 1 again.</t>
+  </si>
+  <si>
+    <t>If bumped on both direction at the same time, it still switches the direction.</t>
+  </si>
+  <si>
+    <t>Ensures that being bumped  when the ground reappears while still falling does not affect the walking direction.</t>
+  </si>
+  <si>
+    <t>Ensures that being bumped in the same cycle as ground disappears (but not yet falling) does not affect the walking direction.</t>
+  </si>
+  <si>
+    <t>Ensures that being bumped while falling does not affect the walking direction.</t>
+  </si>
+  <si>
+    <t>This ensures that Lemming when reaches ground after falling, walks in right direction as before.</t>
   </si>
 </sst>
 </file>
@@ -153,7 +198,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -161,13 +206,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -508,34 +572,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{326842DC-A3A1-4961-ACE6-0AB8F8F2BBEE}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5546875" customWidth="1"/>
-    <col min="3" max="3" width="37.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.53125" customWidth="1"/>
+    <col min="3" max="3" width="37.46484375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.796875" style="1" customWidth="1"/>
     <col min="5" max="5" width="34" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -552,7 +616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -569,7 +633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -586,7 +650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -603,7 +667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -620,7 +684,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -637,7 +701,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -652,6 +716,77 @@
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="C13" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="C14" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="C15" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -660,23 +795,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="a70c7802-7691-4102-a14a-6c055a4ac5c7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C4DE3D4C6C05AC4699FE09C9BA39EBAF" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="acfee0372a6d936a4d10bf57b8be789d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a70c7802-7691-4102-a14a-6c055a4ac5c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b410887572646eb17ca1d08290d29ad2" ns3:_="">
     <xsd:import namespace="a70c7802-7691-4102-a14a-6c055a4ac5c7"/>
@@ -858,31 +976,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="a70c7802-7691-4102-a14a-6c055a4ac5c7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E77E0757-D783-4B4B-80A5-E17FD5E27466}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06193334-5ED0-42B4-A160-EBE30045E23D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a70c7802-7691-4102-a14a-6c055a4ac5c7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60EB4237-5F15-4423-BAF6-35B73FA2475A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -900,6 +1011,30 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06193334-5ED0-42B4-A160-EBE30045E23D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a70c7802-7691-4102-a14a-6c055a4ac5c7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E77E0757-D783-4B4B-80A5-E17FD5E27466}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{bcf48bba-4d6f-4dee-a0d2-7df59cc36629}" enabled="0" method="" siteId="{bcf48bba-4d6f-4dee-a0d2-7df59cc36629}" removed="1"/>
